--- a/ACTIVIDAD FINAL - LA CASA DE CHOCOLATE.xlsx
+++ b/ACTIVIDAD FINAL - LA CASA DE CHOCOLATE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TELIRED SAS\SENA\SENA - desarrollo de software\MATEMATICAS\actividades\actividad final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier Narvaez\Desktop\SENA - ADSO\MATEMATICAS\ACTIVIDADES GIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF8CA8E-A31D-4673-A7F8-2DD0A4080033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63EC0DC-0BC6-4699-AF51-925C28196B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{9C95F963-F389-4FE9-8ABA-90A06D11989E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9C95F963-F389-4FE9-8ABA-90A06D11989E}"/>
   </bookViews>
   <sheets>
     <sheet name="REQUERIMIENTOS " sheetId="3" r:id="rId1"/>
@@ -22,9 +22,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
